--- a/artfynd/A 25320-2024 artfynd.xlsx
+++ b/artfynd/A 25320-2024 artfynd.xlsx
@@ -9977,10 +9977,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118255520</v>
+        <v>118253713</v>
       </c>
       <c r="B73" t="n">
-        <v>97867</v>
+        <v>90522</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9989,35 +9989,34 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -10025,13 +10024,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>361954</v>
+        <v>362065</v>
       </c>
       <c r="R73" t="n">
-        <v>6882150</v>
+        <v>6882019</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10060,7 +10059,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10070,7 +10069,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10097,10 +10096,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118253713</v>
+        <v>118255520</v>
       </c>
       <c r="B74" t="n">
-        <v>90522</v>
+        <v>97867</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10109,34 +10108,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10144,13 +10144,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>362065</v>
+        <v>361954</v>
       </c>
       <c r="R74" t="n">
-        <v>6882019</v>
+        <v>6882150</v>
       </c>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 25320-2024 artfynd.xlsx
+++ b/artfynd/A 25320-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY102"/>
+  <dimension ref="A1:AY109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9476,10 +9476,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118253780</v>
+        <v>118255308</v>
       </c>
       <c r="B69" t="n">
-        <v>57401</v>
+        <v>90522</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9488,43 +9488,34 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -9532,13 +9523,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>362065</v>
+        <v>361957</v>
       </c>
       <c r="R69" t="n">
-        <v>6882019</v>
+        <v>6882015</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9567,7 +9558,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9577,7 +9568,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9604,10 +9595,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118254038</v>
+        <v>118252871</v>
       </c>
       <c r="B70" t="n">
-        <v>90522</v>
+        <v>5186</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9616,34 +9607,40 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>105930</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9651,13 +9648,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>362075</v>
+        <v>362111</v>
       </c>
       <c r="R70" t="n">
-        <v>6882017</v>
+        <v>6882031</v>
       </c>
       <c r="S70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9686,7 +9683,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9696,12 +9693,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Granticka och grynig blåslav på samma gran.</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9728,10 +9720,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118256344</v>
+        <v>118253780</v>
       </c>
       <c r="B71" t="n">
-        <v>57290</v>
+        <v>57401</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9740,20 +9732,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -9763,14 +9755,18 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9780,13 +9776,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>361953</v>
+        <v>362065</v>
       </c>
       <c r="R71" t="n">
-        <v>6882086</v>
+        <v>6882019</v>
       </c>
       <c r="S71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9815,7 +9811,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9825,12 +9821,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på gran</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9857,10 +9848,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118256172</v>
+        <v>118253845</v>
       </c>
       <c r="B72" t="n">
-        <v>97867</v>
+        <v>74596</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9869,35 +9860,30 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9905,10 +9891,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>362008</v>
+        <v>362065</v>
       </c>
       <c r="R72" t="n">
-        <v>6882009</v>
+        <v>6882019</v>
       </c>
       <c r="S72" t="n">
         <v>3</v>
@@ -9940,7 +9926,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9950,7 +9936,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Växer på gammal gran i kanten av en mosse.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9977,10 +9968,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118253713</v>
+        <v>118255520</v>
       </c>
       <c r="B73" t="n">
-        <v>90522</v>
+        <v>97867</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9989,34 +9980,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -10024,13 +10016,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>362065</v>
+        <v>361954</v>
       </c>
       <c r="R73" t="n">
-        <v>6882019</v>
+        <v>6882150</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10059,7 +10051,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10069,7 +10061,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10096,10 +10088,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118255520</v>
+        <v>118253713</v>
       </c>
       <c r="B74" t="n">
-        <v>97867</v>
+        <v>90522</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10108,35 +10100,34 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10144,13 +10135,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>361954</v>
+        <v>362065</v>
       </c>
       <c r="R74" t="n">
-        <v>6882150</v>
+        <v>6882019</v>
       </c>
       <c r="S74" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10179,7 +10170,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10189,7 +10180,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10216,10 +10207,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118255308</v>
+        <v>118252969</v>
       </c>
       <c r="B75" t="n">
-        <v>90522</v>
+        <v>78484</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10232,30 +10223,30 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10263,13 +10254,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>361957</v>
+        <v>362111</v>
       </c>
       <c r="R75" t="n">
-        <v>6882015</v>
+        <v>6882031</v>
       </c>
       <c r="S75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10298,7 +10289,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10308,7 +10299,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10335,10 +10326,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118252969</v>
+        <v>118256172</v>
       </c>
       <c r="B76" t="n">
-        <v>78484</v>
+        <v>97867</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10347,34 +10338,35 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10382,10 +10374,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>362111</v>
+        <v>362008</v>
       </c>
       <c r="R76" t="n">
-        <v>6882031</v>
+        <v>6882009</v>
       </c>
       <c r="S76" t="n">
         <v>3</v>
@@ -10417,7 +10409,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10427,7 +10419,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10454,10 +10446,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118253845</v>
+        <v>118254038</v>
       </c>
       <c r="B77" t="n">
-        <v>74596</v>
+        <v>90522</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10470,25 +10462,29 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
@@ -10497,13 +10493,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>362065</v>
+        <v>362075</v>
       </c>
       <c r="R77" t="n">
-        <v>6882019</v>
+        <v>6882017</v>
       </c>
       <c r="S77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10532,7 +10528,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10542,12 +10538,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Växer på gammal gran i kanten av en mosse.</t>
+          <t>Granticka och grynig blåslav på samma gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10574,10 +10570,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118252871</v>
+        <v>118256344</v>
       </c>
       <c r="B78" t="n">
-        <v>5186</v>
+        <v>57290</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10586,20 +10582,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -10612,12 +10608,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -10627,13 +10622,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>362111</v>
+        <v>361953</v>
       </c>
       <c r="R78" t="n">
-        <v>6882031</v>
+        <v>6882086</v>
       </c>
       <c r="S78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10662,7 +10657,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10672,7 +10667,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10699,10 +10699,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118341337</v>
+        <v>118341987</v>
       </c>
       <c r="B79" t="n">
-        <v>104925</v>
+        <v>90522</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10711,50 +10711,45 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kokällbäckmyren, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>361674</v>
+        <v>361884</v>
       </c>
       <c r="R79" t="n">
-        <v>6882227</v>
+        <v>6882311</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10786,7 +10781,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10796,12 +10791,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Stort bestånd med ögonpyrola inom ett område av ca 3 kvm. Fuktig miljö. Barrnaturskog.</t>
+          <t>Växer på gammal gran. Fjällnära skog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10821,7 +10816,22 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog.</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10839,10 +10849,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118341001</v>
+        <v>118340691</v>
       </c>
       <c r="B80" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10855,48 +10865,45 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>362320</v>
+        <v>362270</v>
       </c>
       <c r="R80" t="n">
-        <v>6882282</v>
+        <v>6882100</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10925,7 +10932,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10935,12 +10942,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Granar draperade med garnlav.</t>
+          <t>Färska hackmärken på gran i fjällnära skog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10949,7 +10956,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -10961,21 +10967,6 @@
       <c r="AI80" t="inlineStr">
         <is>
           <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10993,7 +10984,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118346034</v>
+        <v>118340595</v>
       </c>
       <c r="B81" t="n">
         <v>57290</v>
@@ -11031,20 +11022,20 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>361951</v>
+        <v>362281</v>
       </c>
       <c r="R81" t="n">
-        <v>6882057</v>
+        <v>6882106</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -11071,27 +11062,27 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre hackmärken på gammal gran i fjällnaturskog</t>
+          <t>färska hackmärken på gatan. Fjällnära skog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11128,10 +11119,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118342123</v>
+        <v>118341422</v>
       </c>
       <c r="B82" t="n">
-        <v>78221</v>
+        <v>57290</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11144,26 +11135,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -11171,10 +11167,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>361939</v>
+        <v>361795</v>
       </c>
       <c r="R82" t="n">
-        <v>6882167</v>
+        <v>6882221</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -11206,7 +11202,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11216,12 +11212,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>växer på gammal kolad silverstubbe av tall i barrnaturskog.</t>
+          <t>Färska hackmärken på gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11230,7 +11226,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -11242,21 +11237,6 @@
       <c r="AI82" t="inlineStr">
         <is>
           <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11274,10 +11254,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118341755</v>
+        <v>118347381</v>
       </c>
       <c r="B83" t="n">
-        <v>57290</v>
+        <v>97750</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11286,46 +11266,50 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>361818</v>
+        <v>361988</v>
       </c>
       <c r="R83" t="n">
-        <v>6882272</v>
+        <v>6881972</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -11357,7 +11341,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11367,12 +11351,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Färska hackmnärken på grov gammal gran i fjällnära skog.</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11381,6 +11360,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -11391,7 +11371,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Grannaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11409,10 +11389,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118340481</v>
+        <v>118347475</v>
       </c>
       <c r="B84" t="n">
-        <v>57290</v>
+        <v>74596</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11425,31 +11405,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11457,13 +11432,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>362275</v>
+        <v>361972</v>
       </c>
       <c r="R84" t="n">
-        <v>6882133</v>
+        <v>6881963</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11487,27 +11462,27 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fjällnära skog.</t>
+          <t>Växer på gammal gran i naturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11516,6 +11491,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -11544,10 +11520,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118340920</v>
+        <v>118349286</v>
       </c>
       <c r="B85" t="n">
-        <v>57290</v>
+        <v>97867</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11556,35 +11532,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -11592,13 +11568,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>362284</v>
+        <v>361946</v>
       </c>
       <c r="R85" t="n">
-        <v>6882361</v>
+        <v>6881978</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11622,27 +11598,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken. Skogen är avverkningsanmäld. Gran med hackmärken inom anmälan. Se bild</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11651,6 +11622,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -11661,7 +11633,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>barrnaturskog. Fjällnära</t>
+          <t>Grannaturskog. fjällnära</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11679,10 +11651,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118340027</v>
+        <v>118342123</v>
       </c>
       <c r="B86" t="n">
-        <v>97750</v>
+        <v>78221</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11691,57 +11663,44 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220093</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>362000</v>
+        <v>361939</v>
       </c>
       <c r="R86" t="n">
-        <v>6881981</v>
+        <v>6882167</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11765,27 +11724,27 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster. Hör förekomst av ögonpyrola och andra kärlväxter.</t>
+          <t>växer på gammal kolad silverstubbe av tall i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11805,7 +11764,22 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11823,7 +11797,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118340168</v>
+        <v>118341337</v>
       </c>
       <c r="B87" t="n">
         <v>104925</v>
@@ -11858,7 +11832,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11866,26 +11840,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>362000</v>
+        <v>361674</v>
       </c>
       <c r="R87" t="n">
-        <v>6881981</v>
+        <v>6882227</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11909,27 +11879,27 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster. Hög förekomst av ögonpyrola och andra kärlväxter.</t>
+          <t>Stort bestånd med ögonpyrola inom ett område av ca 3 kvm. Fuktig miljö. Barrnaturskog.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11949,7 +11919,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>gransumpskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11967,10 +11937,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118346113</v>
+        <v>118340285</v>
       </c>
       <c r="B88" t="n">
-        <v>57290</v>
+        <v>97867</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11979,49 +11949,57 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>361968</v>
+        <v>361983</v>
       </c>
       <c r="R88" t="n">
-        <v>6882052</v>
+        <v>6881980</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -12045,27 +12023,27 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Äldre hackmärken på gammal gran.</t>
+          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12074,6 +12052,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -12084,7 +12063,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Grannaturskog.</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12102,10 +12081,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118349286</v>
+        <v>118340481</v>
       </c>
       <c r="B89" t="n">
-        <v>97867</v>
+        <v>57290</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12114,49 +12093,49 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>361946</v>
+        <v>362275</v>
       </c>
       <c r="R89" t="n">
-        <v>6881978</v>
+        <v>6882133</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -12180,22 +12159,27 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på gran i fjällnära skog.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12204,7 +12188,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -12215,7 +12198,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Grannaturskog. fjällnära</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12233,10 +12216,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118347475</v>
+        <v>118346113</v>
       </c>
       <c r="B90" t="n">
-        <v>74596</v>
+        <v>57290</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12249,40 +12232,45 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>361972</v>
+        <v>361968</v>
       </c>
       <c r="R90" t="n">
-        <v>6881963</v>
+        <v>6882052</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -12311,7 +12299,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -12321,12 +12309,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Växer på gammal gran i naturskog. Fjällnära</t>
+          <t>Äldre hackmärken på gammal gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12335,7 +12323,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -12346,7 +12333,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Grannaturskog.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12364,7 +12351,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118340691</v>
+        <v>118346034</v>
       </c>
       <c r="B91" t="n">
         <v>57290</v>
@@ -12402,23 +12389,23 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>362270</v>
+        <v>361951</v>
       </c>
       <c r="R91" t="n">
-        <v>6882100</v>
+        <v>6882057</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12442,27 +12429,27 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fjällnära skog</t>
+          <t>Äldre hackmärken på gammal gran i fjällnaturskog</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12499,10 +12486,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118341987</v>
+        <v>118341001</v>
       </c>
       <c r="B92" t="n">
-        <v>90522</v>
+        <v>78484</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12515,41 +12502,45 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kokällbäckmyren, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>361884</v>
+        <v>362320</v>
       </c>
       <c r="R92" t="n">
-        <v>6882311</v>
+        <v>6882282</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -12576,27 +12567,27 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Växer på gammal gran. Fjällnära skog</t>
+          <t>Granar draperade med garnlav.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12616,7 +12607,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Barrnaturskog.</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -12649,10 +12640,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118347381</v>
+        <v>118340920</v>
       </c>
       <c r="B93" t="n">
-        <v>97750</v>
+        <v>57290</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12661,50 +12652,46 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>361988</v>
+        <v>362284</v>
       </c>
       <c r="R93" t="n">
-        <v>6881972</v>
+        <v>6882361</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -12731,22 +12718,27 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken. Skogen är avverkningsanmäld. Gran med hackmärken inom anmälan. Se bild</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12755,7 +12747,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -12766,7 +12757,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Grannaturskog. Fjällnära</t>
+          <t>barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12784,10 +12775,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118341422</v>
+        <v>118340526</v>
       </c>
       <c r="B94" t="n">
-        <v>57290</v>
+        <v>90430</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12800,42 +12791,41 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>3242</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>361795</v>
+        <v>362269</v>
       </c>
       <c r="R94" t="n">
-        <v>6882221</v>
+        <v>6882132</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -12862,27 +12852,27 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran</t>
+          <t>Växer på undersida av tallgren från gammal tall. Fjällnära skog.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12891,6 +12881,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -12902,6 +12893,21 @@
       <c r="AI94" t="inlineStr">
         <is>
           <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12919,10 +12925,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118340285</v>
+        <v>118340027</v>
       </c>
       <c r="B95" t="n">
-        <v>97867</v>
+        <v>97750</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12935,26 +12941,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -12975,10 +12981,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>361983</v>
+        <v>362000</v>
       </c>
       <c r="R95" t="n">
-        <v>6881980</v>
+        <v>6881981</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -13025,7 +13031,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster.</t>
+          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster. Hör förekomst av ögonpyrola och andra kärlväxter.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13063,10 +13069,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118342015</v>
+        <v>118341755</v>
       </c>
       <c r="B96" t="n">
-        <v>90469</v>
+        <v>57290</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13075,45 +13081,46 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Kokällbäckmyren, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>361893</v>
+        <v>361818</v>
       </c>
       <c r="R96" t="n">
-        <v>6882314</v>
+        <v>6882272</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -13145,7 +13152,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -13155,12 +13162,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Växer på undersida av kolad tallåga.</t>
+          <t>Färska hackmnärken på grov gammal gran i fjällnära skog.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13169,7 +13176,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -13180,22 +13186,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Barrnaturskog. fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13348,10 +13339,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118340595</v>
+        <v>118342015</v>
       </c>
       <c r="B98" t="n">
-        <v>57290</v>
+        <v>90469</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13360,46 +13351,45 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Kokällbäckmyren, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>362281</v>
+        <v>361893</v>
       </c>
       <c r="R98" t="n">
-        <v>6882106</v>
+        <v>6882314</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -13426,27 +13416,27 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>färska hackmärken på gatan. Fjällnära skog</t>
+          <t>Växer på undersida av kolad tallåga.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13455,6 +13445,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -13465,7 +13456,22 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog. fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13483,10 +13489,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118340526</v>
+        <v>118340168</v>
       </c>
       <c r="B99" t="n">
-        <v>90430</v>
+        <v>104925</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13495,34 +13501,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3242</v>
+        <v>221725</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -13530,13 +13545,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>362269</v>
+        <v>362000</v>
       </c>
       <c r="R99" t="n">
-        <v>6882132</v>
+        <v>6881981</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -13560,27 +13575,27 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Växer på undersida av tallgren från gammal tall. Fjällnära skog.</t>
+          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster. Hög förekomst av ögonpyrola och andra kärlväxter.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13600,22 +13615,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>gransumpskog</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13633,7 +13633,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118254049</v>
+        <v>118253309</v>
       </c>
       <c r="B100" t="n">
         <v>78566</v>
@@ -13676,13 +13676,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>362065</v>
+        <v>362077</v>
       </c>
       <c r="R100" t="n">
-        <v>6882019</v>
+        <v>6882043</v>
       </c>
       <c r="S100" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13749,7 +13749,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118253309</v>
+        <v>118254049</v>
       </c>
       <c r="B101" t="n">
         <v>78566</v>
@@ -13792,13 +13792,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>362077</v>
+        <v>362065</v>
       </c>
       <c r="R101" t="n">
-        <v>6882043</v>
+        <v>6882019</v>
       </c>
       <c r="S101" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13998,6 +13998,846 @@
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>118877392</v>
+      </c>
+      <c r="B103" t="n">
+        <v>78566</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>864</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Sälderbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>362014</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6882152</v>
+      </c>
+      <c r="S103" t="n">
+        <v>3</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>118877146</v>
+      </c>
+      <c r="B104" t="n">
+        <v>90947</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Sälderbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>362014</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6882152</v>
+      </c>
+      <c r="S104" t="n">
+        <v>3</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Växer på grov granlåga i fuktig grannnaturskog. Skogen planeras höggallras. Fjällnära skog.</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>118877205</v>
+      </c>
+      <c r="B105" t="n">
+        <v>90788</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>658</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Sälderbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>362014</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6882152</v>
+      </c>
+      <c r="S105" t="n">
+        <v>3</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Växer på grov granlåga tillsammans med rynkskinn. Fjällnära grannaturskog som planeras höggallras. Fuktig lokalmiljö.</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>118876544</v>
+      </c>
+      <c r="B106" t="n">
+        <v>5165</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Sälderbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>362025</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6882099</v>
+      </c>
+      <c r="S106" t="n">
+        <v>4</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre gnagspår på kjolgran i barrnaturskog. Skogen är avverkningsanmäld</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>118878493</v>
+      </c>
+      <c r="B107" t="n">
+        <v>74596</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Sälderbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>362012</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6882222</v>
+      </c>
+      <c r="S107" t="n">
+        <v>3</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Växer på mycket grov gammal gran i fuktig lokalmiljö med vätor. Skogen är avverkningsanmäld</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>118877720</v>
+      </c>
+      <c r="B108" t="n">
+        <v>90522</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Sälderbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>361983</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6882182</v>
+      </c>
+      <c r="S108" t="n">
+        <v>2</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>118877748</v>
+      </c>
+      <c r="B109" t="n">
+        <v>96801</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Sälderbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>361983</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6882182</v>
+      </c>
+      <c r="S109" t="n">
+        <v>6</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25320-2024 artfynd.xlsx
+++ b/artfynd/A 25320-2024 artfynd.xlsx
@@ -11389,10 +11389,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118347475</v>
+        <v>118349286</v>
       </c>
       <c r="B84" t="n">
-        <v>74596</v>
+        <v>97867</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11401,41 +11401,46 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>361972</v>
+        <v>361946</v>
       </c>
       <c r="R84" t="n">
-        <v>6881963</v>
+        <v>6881978</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11480,11 +11485,6 @@
           <t>16:30</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Växer på gammal gran i naturskog. Fjällnära</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Grannaturskog. fjällnära</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11520,10 +11520,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118349286</v>
+        <v>118347475</v>
       </c>
       <c r="B85" t="n">
-        <v>97867</v>
+        <v>74596</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11532,46 +11532,41 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>361946</v>
+        <v>361972</v>
       </c>
       <c r="R85" t="n">
-        <v>6881978</v>
+        <v>6881963</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11616,6 +11611,11 @@
           <t>16:30</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Växer på gammal gran i naturskog. Fjällnära</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -11633,7 +11633,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Grannaturskog. fjällnära</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -12925,10 +12925,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118340027</v>
+        <v>118341755</v>
       </c>
       <c r="B95" t="n">
-        <v>97750</v>
+        <v>57290</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12937,57 +12937,49 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>362000</v>
+        <v>361818</v>
       </c>
       <c r="R95" t="n">
-        <v>6881981</v>
+        <v>6882272</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -13011,27 +13003,27 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster. Hör förekomst av ögonpyrola och andra kärlväxter.</t>
+          <t>Färska hackmnärken på grov gammal gran i fjällnära skog.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13040,7 +13032,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -13051,7 +13042,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13069,10 +13060,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118341755</v>
+        <v>118340027</v>
       </c>
       <c r="B96" t="n">
-        <v>57290</v>
+        <v>97750</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13081,49 +13072,57 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>361818</v>
+        <v>362000</v>
       </c>
       <c r="R96" t="n">
-        <v>6882272</v>
+        <v>6881981</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -13147,27 +13146,27 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Färska hackmnärken på grov gammal gran i fjällnära skog.</t>
+          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster. Hör förekomst av ögonpyrola och andra kärlväxter.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13176,6 +13175,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>

--- a/artfynd/A 25320-2024 artfynd.xlsx
+++ b/artfynd/A 25320-2024 artfynd.xlsx
@@ -10699,10 +10699,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118341987</v>
+        <v>118340526</v>
       </c>
       <c r="B79" t="n">
-        <v>90522</v>
+        <v>90430</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10715,21 +10715,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>3242</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10742,14 +10742,14 @@
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kokällbäckmyren, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>361884</v>
+        <v>362269</v>
       </c>
       <c r="R79" t="n">
-        <v>6882311</v>
+        <v>6882132</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10776,27 +10776,27 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Växer på gammal gran. Fjällnära skog</t>
+          <t>Växer på undersida av tallgren från gammal tall. Fjällnära skog.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10816,22 +10816,22 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Barrnaturskog.</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10849,7 +10849,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118340691</v>
+        <v>118341949</v>
       </c>
       <c r="B80" t="n">
         <v>57290</v>
@@ -10893,17 +10893,17 @@
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>362270</v>
+        <v>361835</v>
       </c>
       <c r="R80" t="n">
-        <v>6882100</v>
+        <v>6882285</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10927,27 +10927,27 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fjällnära skog</t>
+          <t>Färska hackmärken på gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11119,10 +11119,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118341422</v>
+        <v>118340027</v>
       </c>
       <c r="B82" t="n">
-        <v>57290</v>
+        <v>97750</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11131,49 +11131,57 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>361795</v>
+        <v>362000</v>
       </c>
       <c r="R82" t="n">
-        <v>6882221</v>
+        <v>6881981</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11197,27 +11205,27 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran</t>
+          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster. Hör förekomst av ögonpyrola och andra kärlväxter.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11226,6 +11234,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -11236,7 +11245,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11254,10 +11263,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118347381</v>
+        <v>118340481</v>
       </c>
       <c r="B83" t="n">
-        <v>97750</v>
+        <v>57290</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11266,39 +11275,35 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -11306,10 +11311,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>361988</v>
+        <v>362275</v>
       </c>
       <c r="R83" t="n">
-        <v>6881972</v>
+        <v>6882133</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -11336,22 +11341,27 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på gran i fjällnära skog.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11360,7 +11370,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -11371,7 +11380,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Grannaturskog. Fjällnära</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11389,10 +11398,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118349286</v>
+        <v>118341987</v>
       </c>
       <c r="B84" t="n">
-        <v>97867</v>
+        <v>90522</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11401,49 +11410,48 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kokällbäckmyren, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>361946</v>
+        <v>361884</v>
       </c>
       <c r="R84" t="n">
-        <v>6881978</v>
+        <v>6882311</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11472,7 +11480,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11482,7 +11490,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Växer på gammal gran. Fjällnära skog</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11502,7 +11515,22 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Grannaturskog. fjällnära</t>
+          <t>Barrnaturskog.</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11651,10 +11679,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118342123</v>
+        <v>118341422</v>
       </c>
       <c r="B86" t="n">
-        <v>78221</v>
+        <v>57290</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11667,26 +11695,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -11694,10 +11727,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>361939</v>
+        <v>361795</v>
       </c>
       <c r="R86" t="n">
-        <v>6882167</v>
+        <v>6882221</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -11729,7 +11762,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11739,12 +11772,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>växer på gammal kolad silverstubbe av tall i barrnaturskog.</t>
+          <t>Färska hackmärken på gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11753,7 +11786,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -11765,21 +11797,6 @@
       <c r="AI86" t="inlineStr">
         <is>
           <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11797,10 +11814,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118341337</v>
+        <v>118341755</v>
       </c>
       <c r="B87" t="n">
-        <v>104925</v>
+        <v>57290</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11809,39 +11826,35 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -11849,10 +11862,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>361674</v>
+        <v>361818</v>
       </c>
       <c r="R87" t="n">
-        <v>6882227</v>
+        <v>6882272</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -11884,7 +11897,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11894,12 +11907,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Stort bestånd med ögonpyrola inom ett område av ca 3 kvm. Fuktig miljö. Barrnaturskog.</t>
+          <t>Färska hackmnärken på grov gammal gran i fjällnära skog.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11908,7 +11921,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -11937,10 +11949,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118340285</v>
+        <v>118346113</v>
       </c>
       <c r="B88" t="n">
-        <v>97867</v>
+        <v>57290</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11949,57 +11961,49 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>361983</v>
+        <v>361968</v>
       </c>
       <c r="R88" t="n">
-        <v>6881980</v>
+        <v>6882052</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -12023,27 +12027,27 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster.</t>
+          <t>Äldre hackmärken på gammal gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12052,7 +12056,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -12063,7 +12066,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Grannaturskog.</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12081,7 +12084,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118340481</v>
+        <v>118346034</v>
       </c>
       <c r="B89" t="n">
         <v>57290</v>
@@ -12119,20 +12122,20 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>362275</v>
+        <v>361951</v>
       </c>
       <c r="R89" t="n">
-        <v>6882133</v>
+        <v>6882057</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -12159,27 +12162,27 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fjällnära skog.</t>
+          <t>Äldre hackmärken på gammal gran i fjällnaturskog</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12216,7 +12219,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118346113</v>
+        <v>118340920</v>
       </c>
       <c r="B90" t="n">
         <v>57290</v>
@@ -12254,7 +12257,7 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -12264,10 +12267,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>361968</v>
+        <v>362284</v>
       </c>
       <c r="R90" t="n">
-        <v>6882052</v>
+        <v>6882361</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -12294,27 +12297,27 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Äldre hackmärken på gammal gran.</t>
+          <t>Färska och äldre hackmärken. Skogen är avverkningsanmäld. Gran med hackmärken inom anmälan. Se bild</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12333,7 +12336,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Grannaturskog.</t>
+          <t>barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12351,7 +12354,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118346034</v>
+        <v>118340691</v>
       </c>
       <c r="B91" t="n">
         <v>57290</v>
@@ -12389,23 +12392,23 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>361951</v>
+        <v>362270</v>
       </c>
       <c r="R91" t="n">
-        <v>6882057</v>
+        <v>6882100</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12429,27 +12432,27 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Äldre hackmärken på gammal gran i fjällnaturskog</t>
+          <t>Färska hackmärken på gran i fjällnära skog</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12486,10 +12489,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118341001</v>
+        <v>118342015</v>
       </c>
       <c r="B92" t="n">
-        <v>78484</v>
+        <v>90469</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12498,49 +12501,45 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kokällbäckmyren, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>362320</v>
+        <v>361893</v>
       </c>
       <c r="R92" t="n">
-        <v>6882282</v>
+        <v>6882314</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -12567,27 +12566,27 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Granar draperade med garnlav.</t>
+          <t>Växer på undersida av kolad tallåga.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12607,22 +12606,22 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog. fjällnära</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12640,10 +12639,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118340920</v>
+        <v>118347381</v>
       </c>
       <c r="B93" t="n">
-        <v>57290</v>
+        <v>97750</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12652,46 +12651,50 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>362284</v>
+        <v>361988</v>
       </c>
       <c r="R93" t="n">
-        <v>6882361</v>
+        <v>6881972</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -12718,27 +12721,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken. Skogen är avverkningsanmäld. Gran med hackmärken inom anmälan. Se bild</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12747,6 +12745,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -12757,7 +12756,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>barrnaturskog. Fjällnära</t>
+          <t>Grannaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12775,10 +12774,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118340526</v>
+        <v>118341337</v>
       </c>
       <c r="B94" t="n">
-        <v>90430</v>
+        <v>104925</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12787,45 +12786,50 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3242</v>
+        <v>221725</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>362269</v>
+        <v>361674</v>
       </c>
       <c r="R94" t="n">
-        <v>6882132</v>
+        <v>6882227</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -12852,27 +12856,27 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Växer på undersida av tallgren från gammal tall. Fjällnära skog.</t>
+          <t>Stort bestånd med ögonpyrola inom ett område av ca 3 kvm. Fuktig miljö. Barrnaturskog.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12893,21 +12897,6 @@
       <c r="AI94" t="inlineStr">
         <is>
           <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12925,10 +12914,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118341755</v>
+        <v>118342123</v>
       </c>
       <c r="B95" t="n">
-        <v>57290</v>
+        <v>78221</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12941,31 +12930,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -12973,10 +12957,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>361818</v>
+        <v>361939</v>
       </c>
       <c r="R95" t="n">
-        <v>6882272</v>
+        <v>6882167</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -13008,7 +12992,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13018,12 +13002,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Färska hackmnärken på grov gammal gran i fjällnära skog.</t>
+          <t>växer på gammal kolad silverstubbe av tall i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13032,6 +13016,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -13043,6 +13028,21 @@
       <c r="AI95" t="inlineStr">
         <is>
           <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13060,10 +13060,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118340027</v>
+        <v>118341001</v>
       </c>
       <c r="B96" t="n">
-        <v>97750</v>
+        <v>78484</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13072,57 +13072,52 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>362000</v>
+        <v>362320</v>
       </c>
       <c r="R96" t="n">
-        <v>6881981</v>
+        <v>6882282</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -13146,27 +13141,27 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster. Hör förekomst av ögonpyrola och andra kärlväxter.</t>
+          <t>Granar draperade med garnlav.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13186,7 +13181,22 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13204,10 +13214,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118341949</v>
+        <v>118340285</v>
       </c>
       <c r="B97" t="n">
-        <v>57290</v>
+        <v>97867</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13216,49 +13226,57 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>361835</v>
+        <v>361983</v>
       </c>
       <c r="R97" t="n">
-        <v>6882285</v>
+        <v>6881980</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -13282,27 +13300,27 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran</t>
+          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13311,6 +13329,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -13321,7 +13340,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -13339,10 +13358,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118342015</v>
+        <v>118349286</v>
       </c>
       <c r="B98" t="n">
-        <v>90469</v>
+        <v>97867</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13355,44 +13374,45 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kokällbäckmyren, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>361893</v>
+        <v>361946</v>
       </c>
       <c r="R98" t="n">
-        <v>6882314</v>
+        <v>6881978</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -13421,7 +13441,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -13431,12 +13451,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Växer på undersida av kolad tallåga.</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13456,22 +13471,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>Barrnaturskog. fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Grannaturskog. fjällnära</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -14000,10 +14000,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118877392</v>
+        <v>118877146</v>
       </c>
       <c r="B103" t="n">
-        <v>78566</v>
+        <v>90947</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -14012,25 +14012,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>864</v>
+        <v>1209</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -14088,7 +14088,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Växer på grov granlåga i fuktig grannnaturskog. Skogen planeras höggallras. Fjällnära skog.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -14115,10 +14120,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118877146</v>
+        <v>118876544</v>
       </c>
       <c r="B104" t="n">
-        <v>90947</v>
+        <v>5165</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -14127,30 +14132,40 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1209</v>
+        <v>102204</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -14158,13 +14173,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>362014</v>
+        <v>362025</v>
       </c>
       <c r="R104" t="n">
-        <v>6882152</v>
+        <v>6882099</v>
       </c>
       <c r="S104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -14193,7 +14208,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -14203,12 +14218,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Växer på grov granlåga i fuktig grannnaturskog. Skogen planeras höggallras. Fjällnära skog.</t>
+          <t>Äldre gnagspår på kjolgran i barrnaturskog. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -14359,10 +14374,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118876544</v>
+        <v>118877748</v>
       </c>
       <c r="B106" t="n">
-        <v>5165</v>
+        <v>96801</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -14371,40 +14386,31 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>102204</v>
+        <v>221945</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -14412,13 +14418,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>362025</v>
+        <v>361983</v>
       </c>
       <c r="R106" t="n">
-        <v>6882099</v>
+        <v>6882182</v>
       </c>
       <c r="S106" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -14447,7 +14453,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14457,12 +14463,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Äldre gnagspår på kjolgran i barrnaturskog. Skogen är avverkningsanmäld</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14609,10 +14610,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118877720</v>
+        <v>118877392</v>
       </c>
       <c r="B108" t="n">
-        <v>90522</v>
+        <v>78566</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -14625,21 +14626,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -14652,13 +14653,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>361983</v>
+        <v>362014</v>
       </c>
       <c r="R108" t="n">
-        <v>6882182</v>
+        <v>6882152</v>
       </c>
       <c r="S108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -14687,7 +14688,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14697,7 +14698,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14724,10 +14725,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118877748</v>
+        <v>118877720</v>
       </c>
       <c r="B109" t="n">
-        <v>96801</v>
+        <v>90522</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14736,31 +14737,30 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>6882182</v>
       </c>
       <c r="S109" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14813,7 +14813,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD109" t="b">

--- a/artfynd/A 25320-2024 artfynd.xlsx
+++ b/artfynd/A 25320-2024 artfynd.xlsx
@@ -10699,10 +10699,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118340526</v>
+        <v>118347475</v>
       </c>
       <c r="B79" t="n">
-        <v>90430</v>
+        <v>74603</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10715,29 +10715,25 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3242</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
@@ -10746,13 +10742,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>362269</v>
+        <v>361972</v>
       </c>
       <c r="R79" t="n">
-        <v>6882132</v>
+        <v>6881963</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10776,27 +10772,27 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Växer på undersida av tallgren från gammal tall. Fjällnära skog.</t>
+          <t>Växer på gammal gran i naturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10817,21 +10813,6 @@
       <c r="AI79" t="inlineStr">
         <is>
           <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10849,10 +10830,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118341949</v>
+        <v>118342123</v>
       </c>
       <c r="B80" t="n">
-        <v>57290</v>
+        <v>78228</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10865,31 +10846,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10897,10 +10873,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>361835</v>
+        <v>361939</v>
       </c>
       <c r="R80" t="n">
-        <v>6882285</v>
+        <v>6882167</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10932,7 +10908,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10942,12 +10918,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran</t>
+          <t>växer på gammal kolad silverstubbe av tall i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10956,6 +10932,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -10967,6 +10944,21 @@
       <c r="AI80" t="inlineStr">
         <is>
           <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10984,10 +10976,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118340595</v>
+        <v>118342015</v>
       </c>
       <c r="B81" t="n">
-        <v>57290</v>
+        <v>90476</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10996,46 +10988,45 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Kokällbäckmyren, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>362281</v>
+        <v>361893</v>
       </c>
       <c r="R81" t="n">
-        <v>6882106</v>
+        <v>6882314</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -11062,27 +11053,27 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>färska hackmärken på gatan. Fjällnära skog</t>
+          <t>Växer på undersida av kolad tallåga.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11091,6 +11082,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -11101,7 +11093,22 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog. fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11119,10 +11126,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118340027</v>
+        <v>118341949</v>
       </c>
       <c r="B82" t="n">
-        <v>97750</v>
+        <v>57290</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11131,57 +11138,49 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>362000</v>
+        <v>361835</v>
       </c>
       <c r="R82" t="n">
-        <v>6881981</v>
+        <v>6882285</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11205,27 +11204,27 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster. Hör förekomst av ögonpyrola och andra kärlväxter.</t>
+          <t>Färska hackmärken på gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11234,7 +11233,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -11245,7 +11243,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11263,7 +11261,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118340481</v>
+        <v>118340920</v>
       </c>
       <c r="B83" t="n">
         <v>57290</v>
@@ -11307,14 +11305,14 @@
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>362275</v>
+        <v>362284</v>
       </c>
       <c r="R83" t="n">
-        <v>6882133</v>
+        <v>6882361</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -11361,7 +11359,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fjällnära skog.</t>
+          <t>Färska och äldre hackmärken. Skogen är avverkningsanmäld. Gran med hackmärken inom anmälan. Se bild</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11380,7 +11378,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11398,10 +11396,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118341987</v>
+        <v>118340481</v>
       </c>
       <c r="B84" t="n">
-        <v>90522</v>
+        <v>57290</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11414,41 +11412,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kokällbäckmyren, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>361884</v>
+        <v>362275</v>
       </c>
       <c r="R84" t="n">
-        <v>6882311</v>
+        <v>6882133</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -11475,27 +11474,27 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Växer på gammal gran. Fjällnära skog</t>
+          <t>Färska hackmärken på gran i fjällnära skog.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11504,7 +11503,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -11515,22 +11513,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Barrnaturskog.</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11548,10 +11531,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118347475</v>
+        <v>118346113</v>
       </c>
       <c r="B85" t="n">
-        <v>74596</v>
+        <v>57290</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11564,40 +11547,45 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>361972</v>
+        <v>361968</v>
       </c>
       <c r="R85" t="n">
-        <v>6881963</v>
+        <v>6882052</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11626,7 +11614,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11636,12 +11624,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Växer på gammal gran i naturskog. Fjällnära</t>
+          <t>Äldre hackmärken på gammal gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11650,7 +11638,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -11661,7 +11648,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Grannaturskog.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11814,7 +11801,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118341755</v>
+        <v>118340595</v>
       </c>
       <c r="B87" t="n">
         <v>57290</v>
@@ -11858,14 +11845,14 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>361818</v>
+        <v>362281</v>
       </c>
       <c r="R87" t="n">
-        <v>6882272</v>
+        <v>6882106</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -11892,27 +11879,27 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Färska hackmnärken på grov gammal gran i fjällnära skog.</t>
+          <t>färska hackmärken på gatan. Fjällnära skog</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11949,10 +11936,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118346113</v>
+        <v>118347381</v>
       </c>
       <c r="B88" t="n">
-        <v>57290</v>
+        <v>97757</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11961,46 +11948,50 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>361968</v>
+        <v>361988</v>
       </c>
       <c r="R88" t="n">
-        <v>6882052</v>
+        <v>6881972</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -12032,7 +12023,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -12042,12 +12033,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken på gammal gran.</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12056,6 +12042,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -12066,7 +12053,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Grannaturskog.</t>
+          <t>Grannaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12084,10 +12071,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118346034</v>
+        <v>118349286</v>
       </c>
       <c r="B89" t="n">
-        <v>57290</v>
+        <v>97874</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12096,35 +12083,35 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -12132,13 +12119,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>361951</v>
+        <v>361946</v>
       </c>
       <c r="R89" t="n">
-        <v>6882057</v>
+        <v>6881978</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -12167,7 +12154,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -12177,12 +12164,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken på gammal gran i fjällnaturskog</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12191,6 +12173,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -12201,7 +12184,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Grannaturskog. fjällnära</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12219,10 +12202,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118340920</v>
+        <v>118340168</v>
       </c>
       <c r="B90" t="n">
-        <v>57290</v>
+        <v>104932</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12231,49 +12214,57 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>362284</v>
+        <v>362000</v>
       </c>
       <c r="R90" t="n">
-        <v>6882361</v>
+        <v>6881981</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -12297,27 +12288,27 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken. Skogen är avverkningsanmäld. Gran med hackmärken inom anmälan. Se bild</t>
+          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster. Hög förekomst av ögonpyrola och andra kärlväxter.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12326,6 +12317,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -12336,7 +12328,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>barrnaturskog. Fjällnära</t>
+          <t>gransumpskog</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12354,10 +12346,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118340691</v>
+        <v>118340526</v>
       </c>
       <c r="B91" t="n">
-        <v>57290</v>
+        <v>90437</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12370,31 +12362,30 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>3242</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -12402,13 +12393,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>362270</v>
+        <v>362269</v>
       </c>
       <c r="R91" t="n">
-        <v>6882100</v>
+        <v>6882132</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12452,7 +12443,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fjällnära skog</t>
+          <t>Växer på undersida av tallgren från gammal tall. Fjällnära skog.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12461,6 +12452,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -12472,6 +12464,21 @@
       <c r="AI91" t="inlineStr">
         <is>
           <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12489,10 +12496,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118342015</v>
+        <v>118340285</v>
       </c>
       <c r="B92" t="n">
-        <v>90469</v>
+        <v>97874</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12505,44 +12512,53 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kokällbäckmyren, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>361893</v>
+        <v>361983</v>
       </c>
       <c r="R92" t="n">
-        <v>6882314</v>
+        <v>6881980</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -12566,27 +12582,27 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Växer på undersida av kolad tallåga.</t>
+          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12606,22 +12622,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Barrnaturskog. fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12639,10 +12640,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118347381</v>
+        <v>118341337</v>
       </c>
       <c r="B93" t="n">
-        <v>97750</v>
+        <v>104932</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12655,46 +12656,46 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220093</v>
+        <v>221725</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J93" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>361988</v>
+        <v>361674</v>
       </c>
       <c r="R93" t="n">
-        <v>6881972</v>
+        <v>6882227</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -12726,7 +12727,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12736,7 +12737,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Stort bestånd med ögonpyrola inom ett område av ca 3 kvm. Fuktig miljö. Barrnaturskog.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12756,7 +12762,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Grannaturskog. Fjällnära</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12774,10 +12780,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118341337</v>
+        <v>118341755</v>
       </c>
       <c r="B94" t="n">
-        <v>104925</v>
+        <v>57290</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12786,39 +12792,35 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -12826,10 +12828,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>361674</v>
+        <v>361818</v>
       </c>
       <c r="R94" t="n">
-        <v>6882227</v>
+        <v>6882272</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -12861,7 +12863,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12871,12 +12873,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Stort bestånd med ögonpyrola inom ett område av ca 3 kvm. Fuktig miljö. Barrnaturskog.</t>
+          <t>Färska hackmnärken på grov gammal gran i fjällnära skog.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12885,7 +12887,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -12914,10 +12915,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118342123</v>
+        <v>118340027</v>
       </c>
       <c r="B95" t="n">
-        <v>78221</v>
+        <v>97757</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12926,44 +12927,57 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>220093</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>361939</v>
+        <v>362000</v>
       </c>
       <c r="R95" t="n">
-        <v>6882167</v>
+        <v>6881981</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12987,27 +13001,27 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>växer på gammal kolad silverstubbe av tall i barrnaturskog.</t>
+          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster. Hör förekomst av ögonpyrola och andra kärlväxter.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13027,22 +13041,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13060,10 +13059,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118341001</v>
+        <v>118346034</v>
       </c>
       <c r="B96" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13076,32 +13075,29 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -13111,10 +13107,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>362320</v>
+        <v>361951</v>
       </c>
       <c r="R96" t="n">
-        <v>6882282</v>
+        <v>6882057</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -13141,27 +13137,27 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Granar draperade med garnlav.</t>
+          <t>Äldre hackmärken på gammal gran i fjällnaturskog</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13170,7 +13166,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -13182,21 +13177,6 @@
       <c r="AI96" t="inlineStr">
         <is>
           <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13214,10 +13194,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118340285</v>
+        <v>118341001</v>
       </c>
       <c r="B97" t="n">
-        <v>97867</v>
+        <v>78491</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13226,57 +13206,52 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>361983</v>
+        <v>362320</v>
       </c>
       <c r="R97" t="n">
-        <v>6881980</v>
+        <v>6882282</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -13300,27 +13275,27 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster.</t>
+          <t>Granar draperade med garnlav.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13340,7 +13315,22 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -13358,10 +13348,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118349286</v>
+        <v>118340691</v>
       </c>
       <c r="B98" t="n">
-        <v>97867</v>
+        <v>57290</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13370,46 +13360,46 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>361946</v>
+        <v>362270</v>
       </c>
       <c r="R98" t="n">
-        <v>6881978</v>
+        <v>6882100</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13436,22 +13426,27 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på gran i fjällnära skog</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13460,7 +13455,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -13471,7 +13465,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>Grannaturskog. fjällnära</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13489,10 +13483,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118340168</v>
+        <v>118341987</v>
       </c>
       <c r="B99" t="n">
-        <v>104925</v>
+        <v>90529</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13501,57 +13495,48 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Kokällbäckmyren, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>362000</v>
+        <v>361884</v>
       </c>
       <c r="R99" t="n">
-        <v>6881981</v>
+        <v>6882311</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -13575,27 +13560,27 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster. Hög förekomst av ögonpyrola och andra kärlväxter.</t>
+          <t>Växer på gammal gran. Fjällnära skog</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13615,7 +13600,22 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>gransumpskog</t>
+          <t>Barrnaturskog.</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13633,10 +13633,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118253309</v>
+        <v>118254049</v>
       </c>
       <c r="B100" t="n">
-        <v>78566</v>
+        <v>78573</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13676,13 +13676,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>362077</v>
+        <v>362065</v>
       </c>
       <c r="R100" t="n">
-        <v>6882043</v>
+        <v>6882019</v>
       </c>
       <c r="S100" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13749,10 +13749,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118254049</v>
+        <v>118253309</v>
       </c>
       <c r="B101" t="n">
-        <v>78566</v>
+        <v>78573</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13792,13 +13792,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>362065</v>
+        <v>362077</v>
       </c>
       <c r="R101" t="n">
-        <v>6882019</v>
+        <v>6882043</v>
       </c>
       <c r="S101" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -14000,10 +14000,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118877146</v>
+        <v>118877205</v>
       </c>
       <c r="B103" t="n">
-        <v>90947</v>
+        <v>90795</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -14012,29 +14012,33 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
@@ -14078,7 +14082,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -14088,12 +14092,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Växer på grov granlåga i fuktig grannnaturskog. Skogen planeras höggallras. Fjällnära skog.</t>
+          <t>Växer på grov granlåga tillsammans med rynkskinn. Fjällnära grannaturskog som planeras höggallras. Fuktig lokalmiljö.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -14120,10 +14124,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118876544</v>
+        <v>118877748</v>
       </c>
       <c r="B104" t="n">
-        <v>5165</v>
+        <v>96808</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -14132,40 +14136,31 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>102204</v>
+        <v>221945</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -14173,13 +14168,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>362025</v>
+        <v>361983</v>
       </c>
       <c r="R104" t="n">
-        <v>6882099</v>
+        <v>6882182</v>
       </c>
       <c r="S104" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -14208,7 +14203,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -14218,12 +14213,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Äldre gnagspår på kjolgran i barrnaturskog. Skogen är avverkningsanmäld</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -14250,10 +14240,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118877205</v>
+        <v>118877146</v>
       </c>
       <c r="B105" t="n">
-        <v>90788</v>
+        <v>90954</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -14262,33 +14252,29 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
@@ -14332,7 +14318,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -14342,12 +14328,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Växer på grov granlåga tillsammans med rynkskinn. Fjällnära grannaturskog som planeras höggallras. Fuktig lokalmiljö.</t>
+          <t>Växer på grov granlåga i fuktig grannnaturskog. Skogen planeras höggallras. Fjällnära skog.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -14374,10 +14360,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118877748</v>
+        <v>118877392</v>
       </c>
       <c r="B106" t="n">
-        <v>96801</v>
+        <v>78573</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -14386,31 +14372,30 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221945</v>
+        <v>864</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -14418,13 +14403,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>361983</v>
+        <v>362014</v>
       </c>
       <c r="R106" t="n">
-        <v>6882182</v>
+        <v>6882152</v>
       </c>
       <c r="S106" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -14453,7 +14438,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14463,7 +14448,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14490,10 +14475,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118878493</v>
+        <v>118877720</v>
       </c>
       <c r="B107" t="n">
-        <v>74596</v>
+        <v>90529</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -14506,21 +14491,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -14533,13 +14518,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>362012</v>
+        <v>361983</v>
       </c>
       <c r="R107" t="n">
-        <v>6882222</v>
+        <v>6882182</v>
       </c>
       <c r="S107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -14568,7 +14553,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14578,12 +14563,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Växer på mycket grov gammal gran i fuktig lokalmiljö med vätor. Skogen är avverkningsanmäld</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14610,10 +14590,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118877392</v>
+        <v>118876544</v>
       </c>
       <c r="B108" t="n">
-        <v>78566</v>
+        <v>5165</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -14626,26 +14606,36 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>864</v>
+        <v>102204</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -14653,13 +14643,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>362014</v>
+        <v>362025</v>
       </c>
       <c r="R108" t="n">
-        <v>6882152</v>
+        <v>6882099</v>
       </c>
       <c r="S108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -14688,7 +14678,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14698,7 +14688,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Äldre gnagspår på kjolgran i barrnaturskog. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14725,10 +14720,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118877720</v>
+        <v>118878493</v>
       </c>
       <c r="B109" t="n">
-        <v>90522</v>
+        <v>74603</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14741,21 +14736,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -14768,13 +14763,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>361983</v>
+        <v>362012</v>
       </c>
       <c r="R109" t="n">
-        <v>6882182</v>
+        <v>6882222</v>
       </c>
       <c r="S109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -14803,7 +14798,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14813,7 +14808,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Växer på mycket grov gammal gran i fuktig lokalmiljö med vätor. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD109" t="b">

--- a/artfynd/A 25320-2024 artfynd.xlsx
+++ b/artfynd/A 25320-2024 artfynd.xlsx
@@ -13059,10 +13059,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118346034</v>
+        <v>118341001</v>
       </c>
       <c r="B96" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13075,29 +13075,32 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -13107,10 +13110,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>361951</v>
+        <v>362320</v>
       </c>
       <c r="R96" t="n">
-        <v>6882057</v>
+        <v>6882282</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -13137,27 +13140,27 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Äldre hackmärken på gammal gran i fjällnaturskog</t>
+          <t>Granar draperade med garnlav.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13166,6 +13169,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -13177,6 +13181,21 @@
       <c r="AI96" t="inlineStr">
         <is>
           <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13194,10 +13213,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118341001</v>
+        <v>118346034</v>
       </c>
       <c r="B97" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13210,32 +13229,29 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -13245,10 +13261,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>362320</v>
+        <v>361951</v>
       </c>
       <c r="R97" t="n">
-        <v>6882282</v>
+        <v>6882057</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -13275,27 +13291,27 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Granar draperade med garnlav.</t>
+          <t>Äldre hackmärken på gammal gran i fjällnaturskog</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13304,7 +13320,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -13316,21 +13331,6 @@
       <c r="AI97" t="inlineStr">
         <is>
           <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>

--- a/artfynd/A 25320-2024 artfynd.xlsx
+++ b/artfynd/A 25320-2024 artfynd.xlsx
@@ -10699,10 +10699,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118347475</v>
+        <v>118340691</v>
       </c>
       <c r="B79" t="n">
-        <v>74603</v>
+        <v>57290</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10715,26 +10715,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -10742,10 +10747,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>361972</v>
+        <v>362270</v>
       </c>
       <c r="R79" t="n">
-        <v>6881963</v>
+        <v>6882100</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10772,27 +10777,27 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Växer på gammal gran i naturskog. Fjällnära</t>
+          <t>Färska hackmärken på gran i fjällnära skog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10801,7 +10806,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -10830,10 +10834,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118342123</v>
+        <v>118342015</v>
       </c>
       <c r="B80" t="n">
-        <v>78228</v>
+        <v>90476</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10842,41 +10846,45 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kokällbäckmyren, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>361939</v>
+        <v>361893</v>
       </c>
       <c r="R80" t="n">
-        <v>6882167</v>
+        <v>6882314</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10923,7 +10931,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>växer på gammal kolad silverstubbe av tall i barrnaturskog.</t>
+          <t>Växer på undersida av kolad tallåga.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10943,7 +10951,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog. fjällnära</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
@@ -10976,10 +10984,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118342015</v>
+        <v>118340526</v>
       </c>
       <c r="B81" t="n">
-        <v>90476</v>
+        <v>90437</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10988,25 +10996,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11019,14 +11027,14 @@
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kokällbäckmyren, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>361893</v>
+        <v>362269</v>
       </c>
       <c r="R81" t="n">
-        <v>6882314</v>
+        <v>6882132</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -11053,27 +11061,27 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Växer på undersida av kolad tallåga.</t>
+          <t>Växer på undersida av tallgren från gammal tall. Fjällnära skog.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11093,7 +11101,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Barrnaturskog. fjällnära</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -11126,10 +11134,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118341949</v>
+        <v>118340168</v>
       </c>
       <c r="B82" t="n">
-        <v>57290</v>
+        <v>104932</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11138,49 +11146,57 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>361835</v>
+        <v>362000</v>
       </c>
       <c r="R82" t="n">
-        <v>6882285</v>
+        <v>6881981</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11204,27 +11220,27 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran</t>
+          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster. Hög förekomst av ögonpyrola och andra kärlväxter.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11233,6 +11249,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -11243,7 +11260,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>gransumpskog</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11261,10 +11278,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118340920</v>
+        <v>118341987</v>
       </c>
       <c r="B83" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11277,42 +11294,41 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kokällbäckmyren, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>362284</v>
+        <v>361884</v>
       </c>
       <c r="R83" t="n">
-        <v>6882361</v>
+        <v>6882311</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -11339,27 +11355,27 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken. Skogen är avverkningsanmäld. Gran med hackmärken inom anmälan. Se bild</t>
+          <t>Växer på gammal gran. Fjällnära skog</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11368,6 +11384,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -11378,7 +11395,22 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog.</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11396,7 +11428,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118340481</v>
+        <v>118346113</v>
       </c>
       <c r="B84" t="n">
         <v>57290</v>
@@ -11434,20 +11466,20 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>362275</v>
+        <v>361968</v>
       </c>
       <c r="R84" t="n">
-        <v>6882133</v>
+        <v>6882052</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -11474,27 +11506,27 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fjällnära skog.</t>
+          <t>Äldre hackmärken på gammal gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11513,7 +11545,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Grannaturskog.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11531,7 +11563,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118346113</v>
+        <v>118346034</v>
       </c>
       <c r="B85" t="n">
         <v>57290</v>
@@ -11579,10 +11611,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>361968</v>
+        <v>361951</v>
       </c>
       <c r="R85" t="n">
-        <v>6882052</v>
+        <v>6882057</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -11614,7 +11646,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11624,12 +11656,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Äldre hackmärken på gammal gran.</t>
+          <t>Äldre hackmärken på gammal gran i fjällnaturskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11648,7 +11680,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Grannaturskog.</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11666,10 +11698,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118341422</v>
+        <v>118347381</v>
       </c>
       <c r="B86" t="n">
-        <v>57290</v>
+        <v>97757</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11678,46 +11710,50 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>361795</v>
+        <v>361988</v>
       </c>
       <c r="R86" t="n">
-        <v>6882221</v>
+        <v>6881972</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -11749,7 +11785,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11759,12 +11795,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på gran</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11773,6 +11804,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -11783,7 +11815,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Grannaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11801,10 +11833,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118340595</v>
+        <v>118342123</v>
       </c>
       <c r="B87" t="n">
-        <v>57290</v>
+        <v>78228</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -11817,42 +11849,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>362281</v>
+        <v>361939</v>
       </c>
       <c r="R87" t="n">
-        <v>6882106</v>
+        <v>6882167</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -11879,27 +11906,27 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>färska hackmärken på gatan. Fjällnära skog</t>
+          <t>växer på gammal kolad silverstubbe av tall i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11908,6 +11935,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -11919,6 +11947,21 @@
       <c r="AI87" t="inlineStr">
         <is>
           <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11936,7 +11979,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118347381</v>
+        <v>118340027</v>
       </c>
       <c r="B88" t="n">
         <v>97757</v>
@@ -11969,7 +12012,11 @@
           <t>Châtel.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -11988,13 +12035,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>361988</v>
+        <v>362000</v>
       </c>
       <c r="R88" t="n">
-        <v>6881972</v>
+        <v>6881981</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -12018,22 +12065,27 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster. Hör förekomst av ögonpyrola och andra kärlväxter.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12053,7 +12105,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Grannaturskog. Fjällnära</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12071,10 +12123,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118349286</v>
+        <v>118341949</v>
       </c>
       <c r="B89" t="n">
-        <v>97874</v>
+        <v>57290</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12083,49 +12135,49 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>361946</v>
+        <v>361835</v>
       </c>
       <c r="R89" t="n">
-        <v>6881978</v>
+        <v>6882285</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -12154,7 +12206,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -12164,7 +12216,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på gran</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12173,7 +12230,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -12184,7 +12240,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Grannaturskog. fjällnära</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12202,10 +12258,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118340168</v>
+        <v>118340920</v>
       </c>
       <c r="B90" t="n">
-        <v>104932</v>
+        <v>57290</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12214,57 +12270,49 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>362000</v>
+        <v>362284</v>
       </c>
       <c r="R90" t="n">
-        <v>6881981</v>
+        <v>6882361</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -12288,27 +12336,27 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster. Hög förekomst av ögonpyrola och andra kärlväxter.</t>
+          <t>Färska och äldre hackmärken. Skogen är avverkningsanmäld. Gran med hackmärken inom anmälan. Se bild</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12317,7 +12365,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -12328,7 +12375,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>gransumpskog</t>
+          <t>barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12346,10 +12393,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118340526</v>
+        <v>118340595</v>
       </c>
       <c r="B91" t="n">
-        <v>90437</v>
+        <v>57290</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12362,30 +12409,31 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3242</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -12393,10 +12441,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>362269</v>
+        <v>362281</v>
       </c>
       <c r="R91" t="n">
-        <v>6882132</v>
+        <v>6882106</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -12443,7 +12491,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Växer på undersida av tallgren från gammal tall. Fjällnära skog.</t>
+          <t>färska hackmärken på gatan. Fjällnära skog</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12452,7 +12500,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -12464,21 +12511,6 @@
       <c r="AI91" t="inlineStr">
         <is>
           <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12496,10 +12528,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118340285</v>
+        <v>118340481</v>
       </c>
       <c r="B92" t="n">
-        <v>97874</v>
+        <v>57290</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12508,43 +12540,35 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -12552,13 +12576,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>361983</v>
+        <v>362275</v>
       </c>
       <c r="R92" t="n">
-        <v>6881980</v>
+        <v>6882133</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -12582,27 +12606,27 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster.</t>
+          <t>Färska hackmärken på gran i fjällnära skog.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12611,7 +12635,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -12622,7 +12645,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12640,10 +12663,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118341337</v>
+        <v>118349286</v>
       </c>
       <c r="B93" t="n">
-        <v>104932</v>
+        <v>97874</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -12656,28 +12679,24 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -12688,17 +12707,17 @@
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>361674</v>
+        <v>361946</v>
       </c>
       <c r="R93" t="n">
-        <v>6882227</v>
+        <v>6881978</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -12727,7 +12746,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12737,12 +12756,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Stort bestånd med ögonpyrola inom ett område av ca 3 kvm. Fuktig miljö. Barrnaturskog.</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12762,7 +12776,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Grannaturskog. fjällnära</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12780,10 +12794,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118341755</v>
+        <v>118341001</v>
       </c>
       <c r="B94" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -12796,42 +12810,45 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>361818</v>
+        <v>362320</v>
       </c>
       <c r="R94" t="n">
-        <v>6882272</v>
+        <v>6882282</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -12858,27 +12875,27 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Färska hackmnärken på grov gammal gran i fjällnära skog.</t>
+          <t>Granar draperade med garnlav.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12887,6 +12904,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -12898,6 +12916,21 @@
       <c r="AI94" t="inlineStr">
         <is>
           <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12915,10 +12948,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118340027</v>
+        <v>118341422</v>
       </c>
       <c r="B95" t="n">
-        <v>97757</v>
+        <v>57290</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12927,57 +12960,49 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>362000</v>
+        <v>361795</v>
       </c>
       <c r="R95" t="n">
-        <v>6881981</v>
+        <v>6882221</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -13001,27 +13026,27 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster. Hör förekomst av ögonpyrola och andra kärlväxter.</t>
+          <t>Färska hackmärken på gran</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13030,7 +13055,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -13041,7 +13065,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13059,10 +13083,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118341001</v>
+        <v>118341755</v>
       </c>
       <c r="B96" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13075,45 +13099,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>362320</v>
+        <v>361818</v>
       </c>
       <c r="R96" t="n">
-        <v>6882282</v>
+        <v>6882272</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -13140,27 +13161,27 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Granar draperade med garnlav.</t>
+          <t>Färska hackmnärken på grov gammal gran i fjällnära skog.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13169,7 +13190,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -13181,21 +13201,6 @@
       <c r="AI96" t="inlineStr">
         <is>
           <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13213,10 +13218,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118346034</v>
+        <v>118347475</v>
       </c>
       <c r="B97" t="n">
-        <v>57290</v>
+        <v>74603</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13229,45 +13234,40 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>361951</v>
+        <v>361972</v>
       </c>
       <c r="R97" t="n">
-        <v>6882057</v>
+        <v>6881963</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Äldre hackmärken på gammal gran i fjällnaturskog</t>
+          <t>Växer på gammal gran i naturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13320,6 +13320,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -13348,10 +13349,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118340691</v>
+        <v>118341337</v>
       </c>
       <c r="B98" t="n">
-        <v>57290</v>
+        <v>104932</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13360,49 +13361,53 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Stenbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>362270</v>
+        <v>361674</v>
       </c>
       <c r="R98" t="n">
-        <v>6882100</v>
+        <v>6882227</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -13426,27 +13431,27 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fjällnära skog</t>
+          <t>Stort bestånd med ögonpyrola inom ett område av ca 3 kvm. Fuktig miljö. Barrnaturskog.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13455,6 +13460,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -13483,10 +13489,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118341987</v>
+        <v>118340285</v>
       </c>
       <c r="B99" t="n">
-        <v>90529</v>
+        <v>97874</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13495,48 +13501,57 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Kokällbäckmyren, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>361884</v>
+        <v>361983</v>
       </c>
       <c r="R99" t="n">
-        <v>6882311</v>
+        <v>6881980</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -13560,27 +13575,27 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Växer på gammal gran. Fjällnära skog</t>
+          <t>Växer i gransumpskog med beskuggade gamla granar. I skogsmiljön finns rikligt med orkidéer som korallrot och spindelblomster.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13600,22 +13615,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>Barrnaturskog.</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -14124,10 +14124,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118877748</v>
+        <v>118877392</v>
       </c>
       <c r="B104" t="n">
-        <v>96808</v>
+        <v>78573</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -14136,31 +14136,30 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221945</v>
+        <v>864</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -14168,13 +14167,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>361983</v>
+        <v>362014</v>
       </c>
       <c r="R104" t="n">
-        <v>6882182</v>
+        <v>6882152</v>
       </c>
       <c r="S104" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -14203,7 +14202,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -14213,7 +14212,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -14360,10 +14359,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118877392</v>
+        <v>118877720</v>
       </c>
       <c r="B106" t="n">
-        <v>78573</v>
+        <v>90529</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -14376,21 +14375,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -14403,13 +14402,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>362014</v>
+        <v>361983</v>
       </c>
       <c r="R106" t="n">
-        <v>6882152</v>
+        <v>6882182</v>
       </c>
       <c r="S106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -14438,7 +14437,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14448,7 +14447,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14475,10 +14474,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118877720</v>
+        <v>118876544</v>
       </c>
       <c r="B107" t="n">
-        <v>90529</v>
+        <v>5165</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -14491,26 +14490,36 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5432</v>
+        <v>102204</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -14518,13 +14527,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>361983</v>
+        <v>362025</v>
       </c>
       <c r="R107" t="n">
-        <v>6882182</v>
+        <v>6882099</v>
       </c>
       <c r="S107" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -14553,7 +14562,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14563,7 +14572,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Äldre gnagspår på kjolgran i barrnaturskog. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14590,10 +14604,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118876544</v>
+        <v>118878493</v>
       </c>
       <c r="B108" t="n">
-        <v>5165</v>
+        <v>74603</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -14606,36 +14620,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>102204</v>
+        <v>6440</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -14643,13 +14647,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>362025</v>
+        <v>362012</v>
       </c>
       <c r="R108" t="n">
-        <v>6882099</v>
+        <v>6882222</v>
       </c>
       <c r="S108" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -14678,7 +14682,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14688,12 +14692,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Äldre gnagspår på kjolgran i barrnaturskog. Skogen är avverkningsanmäld</t>
+          <t>Växer på mycket grov gammal gran i fuktig lokalmiljö med vätor. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14720,10 +14724,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118878493</v>
+        <v>118877748</v>
       </c>
       <c r="B109" t="n">
-        <v>74603</v>
+        <v>96808</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -14732,30 +14736,31 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -14763,13 +14768,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>362012</v>
+        <v>361983</v>
       </c>
       <c r="R109" t="n">
-        <v>6882222</v>
+        <v>6882182</v>
       </c>
       <c r="S109" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -14798,7 +14803,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14808,12 +14813,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Växer på mycket grov gammal gran i fuktig lokalmiljö med vätor. Skogen är avverkningsanmäld</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD109" t="b">

--- a/artfynd/A 25320-2024 artfynd.xlsx
+++ b/artfynd/A 25320-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118103394</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>118095116</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>118091349</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>118095460</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>118095580</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>118094664</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>118121714</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>118119653</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>118122031</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>118122497</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>118122157</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>118118603</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>118120447</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>118118905</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>118120074</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>118119701</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>118120248</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>118119872</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>118122458</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>118118562</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>118119170</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>118121878</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>118119133</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>118122205</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>118118547</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>118107736</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>118120164</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>118119483</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>118118863</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>118121528</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>118119770</v>
       </c>
       <c r="B55" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>118120388</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>118122435</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>118118450</v>
       </c>
       <c r="B61" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>118121956</v>
       </c>
       <c r="B62" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>118139803</v>
       </c>
       <c r="B64" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>118141612</v>
       </c>
       <c r="B66" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>118256344</v>
       </c>
       <c r="B78" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>118340691</v>
       </c>
       <c r="B79" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>118346113</v>
       </c>
       <c r="B84" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>118346034</v>
       </c>
       <c r="B85" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>118341949</v>
       </c>
       <c r="B89" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>118340920</v>
       </c>
       <c r="B90" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>118340595</v>
       </c>
       <c r="B91" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>118340481</v>
       </c>
       <c r="B92" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>118341422</v>
       </c>
       <c r="B95" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>118341755</v>
       </c>
       <c r="B96" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>118121619</v>
       </c>
       <c r="B102" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
